--- a/формулы.xlsx
+++ b/формулы.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Разработка\Arduino_2024\Вольтметр 15S\vloltmetr_15S_8266_kompensation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Разработка\Arduino_2024\Вольтметр 15S\voltmetr_16S_8266_kompensation\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -50,9 +50,6 @@
     <t>по умолч</t>
   </si>
   <si>
-    <t>С0</t>
-  </si>
-  <si>
     <t>С1</t>
   </si>
   <si>
@@ -87,6 +84,9 @@
   </si>
   <si>
     <t>voltageDividerRatios</t>
+  </si>
+  <si>
+    <t>С10</t>
   </si>
 </sst>
 </file>
@@ -94,7 +94,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="170" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -349,27 +349,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="0" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="170" fontId="0" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -672,7 +672,7 @@
     </row>
     <row r="2" spans="2:14" x14ac:dyDescent="0.3">
       <c r="D2" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E2" s="10"/>
       <c r="F2" s="10"/>
@@ -710,10 +710,10 @@
       <c r="F7" s="12"/>
       <c r="G7" s="12"/>
       <c r="H7" s="12"/>
-      <c r="J7" s="16" t="s">
+      <c r="J7" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="K7" s="24"/>
+      <c r="K7" s="29"/>
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
       <c r="N7" s="4"/>
@@ -732,14 +732,14 @@
       </c>
       <c r="G8" s="5"/>
       <c r="H8" s="5"/>
-      <c r="J8" s="25" t="s">
+      <c r="J8" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="K8" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="L8" s="19" t="s">
         <v>19</v>
-      </c>
-      <c r="K8" s="26" t="s">
-        <v>2</v>
-      </c>
-      <c r="L8" s="20" t="s">
-        <v>20</v>
       </c>
       <c r="M8" s="5"/>
       <c r="N8" s="6"/>
@@ -757,13 +757,13 @@
         <f>D9/((F5*3/1023)*3.3)</f>
         <v>11.781249999999998</v>
       </c>
-      <c r="J9" s="17">
+      <c r="J9" s="16">
         <v>88</v>
       </c>
-      <c r="K9" s="27">
+      <c r="K9" s="25">
         <v>3.4</v>
       </c>
-      <c r="L9" s="21">
+      <c r="L9" s="20">
         <f>(K9*1023)/(3.3*J9)</f>
         <v>11.977272727272728</v>
       </c>
@@ -773,13 +773,13 @@
       </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="J10" s="17">
+      <c r="J10" s="16">
         <v>163</v>
       </c>
-      <c r="K10" s="27">
+      <c r="K10" s="25">
         <v>6.6</v>
       </c>
-      <c r="L10" s="21">
+      <c r="L10" s="20">
         <f t="shared" ref="L10:L18" si="0">(K10*1023)/(3.3*J10)</f>
         <v>12.552147239263803</v>
       </c>
@@ -794,13 +794,13 @@
       <c r="F11" s="5"/>
       <c r="G11" s="5"/>
       <c r="H11" s="5"/>
-      <c r="J11" s="17">
+      <c r="J11" s="16">
         <v>232</v>
       </c>
-      <c r="K11" s="27">
+      <c r="K11" s="25">
         <v>9.6</v>
       </c>
-      <c r="L11" s="21">
+      <c r="L11" s="20">
         <f t="shared" si="0"/>
         <v>12.827586206896552</v>
       </c>
@@ -815,13 +815,13 @@
       <c r="F12" s="5"/>
       <c r="G12" s="5"/>
       <c r="H12" s="5"/>
-      <c r="J12" s="17">
+      <c r="J12" s="16">
         <v>283</v>
       </c>
-      <c r="K12" s="27">
+      <c r="K12" s="25">
         <v>12.6</v>
       </c>
-      <c r="L12" s="21">
+      <c r="L12" s="20">
         <f t="shared" si="0"/>
         <v>13.802120141342757</v>
       </c>
@@ -836,13 +836,13 @@
       <c r="F13" s="5"/>
       <c r="G13" s="5"/>
       <c r="H13" s="5"/>
-      <c r="J13" s="17">
+      <c r="J13" s="16">
         <v>381</v>
       </c>
-      <c r="K13" s="27">
+      <c r="K13" s="25">
         <v>16.2</v>
       </c>
-      <c r="L13" s="21">
+      <c r="L13" s="20">
         <f t="shared" si="0"/>
         <v>13.181102362204724</v>
       </c>
@@ -852,13 +852,13 @@
       </c>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="J14" s="17">
+      <c r="J14" s="16">
         <v>450</v>
       </c>
-      <c r="K14" s="27">
+      <c r="K14" s="25">
         <v>19.2</v>
       </c>
-      <c r="L14" s="21">
+      <c r="L14" s="20">
         <f t="shared" si="0"/>
         <v>13.226666666666667</v>
       </c>
@@ -868,13 +868,13 @@
       </c>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="J15" s="17">
+      <c r="J15" s="16">
         <v>541</v>
       </c>
-      <c r="K15" s="27">
+      <c r="K15" s="25">
         <v>23</v>
       </c>
-      <c r="L15" s="21">
+      <c r="L15" s="20">
         <f t="shared" si="0"/>
         <v>13.179297597042515</v>
       </c>
@@ -884,13 +884,13 @@
       </c>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="J16" s="17">
+      <c r="J16" s="16">
         <v>606</v>
       </c>
-      <c r="K16" s="27">
+      <c r="K16" s="25">
         <v>26.4</v>
       </c>
-      <c r="L16" s="21">
+      <c r="L16" s="20">
         <f t="shared" si="0"/>
         <v>13.504950495049505</v>
       </c>
@@ -900,13 +900,13 @@
       </c>
     </row>
     <row r="17" spans="10:14" x14ac:dyDescent="0.3">
-      <c r="J17" s="17">
+      <c r="J17" s="16">
         <v>714</v>
       </c>
-      <c r="K17" s="27">
+      <c r="K17" s="25">
         <v>29.7</v>
       </c>
-      <c r="L17" s="21">
+      <c r="L17" s="20">
         <f t="shared" si="0"/>
         <v>12.894957983193278</v>
       </c>
@@ -916,46 +916,46 @@
       </c>
     </row>
     <row r="18" spans="10:14" x14ac:dyDescent="0.3">
-      <c r="J18" s="17">
-        <v>619</v>
-      </c>
-      <c r="K18" s="27">
-        <v>33.5</v>
-      </c>
-      <c r="L18" s="21">
+      <c r="J18" s="16">
+        <v>622</v>
+      </c>
+      <c r="K18" s="25">
+        <v>33.4</v>
+      </c>
+      <c r="L18" s="20">
         <f t="shared" si="0"/>
-        <v>16.777059773828757</v>
+        <v>16.646302250803856</v>
       </c>
       <c r="M18" s="5"/>
       <c r="N18" s="6" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19" spans="10:14" x14ac:dyDescent="0.3">
-      <c r="J19" s="18"/>
-      <c r="K19" s="28"/>
-      <c r="L19" s="22"/>
+      <c r="J19" s="17"/>
+      <c r="K19" s="26"/>
+      <c r="L19" s="21"/>
       <c r="M19" s="5"/>
       <c r="N19" s="6"/>
     </row>
     <row r="20" spans="10:14" x14ac:dyDescent="0.3">
-      <c r="J20" s="18"/>
-      <c r="K20" s="28"/>
-      <c r="L20" s="22"/>
+      <c r="J20" s="17"/>
+      <c r="K20" s="26"/>
+      <c r="L20" s="21"/>
       <c r="M20" s="5"/>
       <c r="N20" s="6"/>
     </row>
     <row r="21" spans="10:14" x14ac:dyDescent="0.3">
-      <c r="J21" s="18"/>
-      <c r="K21" s="28"/>
-      <c r="L21" s="22"/>
+      <c r="J21" s="17"/>
+      <c r="K21" s="26"/>
+      <c r="L21" s="21"/>
       <c r="M21" s="5"/>
       <c r="N21" s="6"/>
     </row>
     <row r="22" spans="10:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="J22" s="19"/>
-      <c r="K22" s="29"/>
-      <c r="L22" s="23"/>
+      <c r="J22" s="18"/>
+      <c r="K22" s="27"/>
+      <c r="L22" s="22"/>
       <c r="M22" s="7"/>
       <c r="N22" s="8"/>
     </row>

--- a/формулы.xlsx
+++ b/формулы.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Разработка\Arduino_2024\Вольтметр 15S\voltmetr_16S_8266_kompensation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Разработка\Arduino_2024\+004_Voltmetr_10S_8266_kompensation_Display_1610_Encoder\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="25">
   <si>
     <t>sum / 3.0 / 1023.0) * 3.3 * voltageDividerRatios[channel];</t>
   </si>
@@ -87,6 +87,18 @@
   </si>
   <si>
     <t>С10</t>
+  </si>
+  <si>
+    <t>коэффициент = Целевое напряжение / ((Коэффициент / 1023) * 3.3)</t>
+  </si>
+  <si>
+    <t>напр</t>
+  </si>
+  <si>
+    <t>кооф</t>
+  </si>
+  <si>
+    <t>целевое</t>
   </si>
 </sst>
 </file>
@@ -331,7 +343,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -370,6 +382,7 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -679,6 +692,11 @@
       <c r="G2" s="10"/>
       <c r="H2" s="10"/>
     </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="D3" t="s">
+        <v>21</v>
+      </c>
+    </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>3</v>
@@ -758,14 +776,14 @@
         <v>11.781249999999998</v>
       </c>
       <c r="J9" s="16">
-        <v>88</v>
+        <v>385</v>
       </c>
       <c r="K9" s="25">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="L9" s="20">
         <f>(K9*1023)/(3.3*J9)</f>
-        <v>11.977272727272728</v>
+        <v>2.4155844155844157</v>
       </c>
       <c r="M9" s="5"/>
       <c r="N9" s="6" t="s">
@@ -810,11 +828,18 @@
       </c>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
+      <c r="D12" t="s">
+        <v>23</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F12" t="s">
+        <v>24</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>23</v>
+      </c>
       <c r="J12" s="16">
         <v>283</v>
       </c>
@@ -831,11 +856,23 @@
       </c>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
+      <c r="B13" s="30">
+        <v>30</v>
+      </c>
+      <c r="D13" s="5">
+        <v>4.7</v>
+      </c>
+      <c r="E13">
+        <f>(B13/1023)*3.3*D13</f>
+        <v>0.45483870967741935</v>
+      </c>
+      <c r="F13">
+        <v>4.13</v>
+      </c>
+      <c r="H13">
+        <f>F13/((B13/1023)*3.3)</f>
+        <v>42.676666666666669</v>
+      </c>
       <c r="J13" s="16">
         <v>381</v>
       </c>
@@ -852,6 +889,21 @@
       </c>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B14">
+        <v>329</v>
+      </c>
+      <c r="D14" s="5"/>
+      <c r="E14">
+        <f>((B14/1023)*3.3*D14)-E13</f>
+        <v>-0.45483870967741935</v>
+      </c>
+      <c r="F14">
+        <v>4.12</v>
+      </c>
+      <c r="H14">
+        <f>(F14)/((B14/1023)*3.3)</f>
+        <v>3.8820668693009122</v>
+      </c>
       <c r="J14" s="16">
         <v>450</v>
       </c>
